--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/HeroDisplay.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/HeroDisplay.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="HeroDisplay" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -95,10 +95,19 @@
     <t>暴风雪</t>
   </si>
   <si>
-    <t>Aniao_HeroDisplay</t>
+    <t>Axiong_HeroDisplay</t>
   </si>
   <si>
     <t>寒冰箭</t>
+  </si>
+  <si>
+    <t>Axi_HeroDisplay</t>
+  </si>
+  <si>
+    <t>Atu_HeroDisplay</t>
+  </si>
+  <si>
+    <t>Aqi_HeroDisplay</t>
   </si>
 </sst>
 </file>
@@ -572,154 +581,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1059,130 +1068,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="30.2833333333333" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="0">
+    <row r="5" spans="1:6">
+      <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="0">
+    <row r="6" spans="1:6">
+      <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="0">
+    <row r="7" spans="1:6">
+      <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:6">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:6">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1190,9 +1251,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>